--- a/시험수수료표.xlsx
+++ b/시험수수료표.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4506"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView xWindow="-15" yWindow="525" windowWidth="16245" windowHeight="5805" tabRatio="840"/>
+    <workbookView xWindow="-15" yWindow="525" windowWidth="16245" windowHeight="5805" tabRatio="840" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="수수료표" sheetId="44" r:id="rId1"/>
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="74">
   <si>
     <t>시험명</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -307,6 +307,10 @@
   </si>
   <si>
     <t>기본가격</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CHOIGODAEUN</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -316,7 +320,7 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="2">
     <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="#,##0_);[Red]\(#,##0\)"/>
+    <numFmt numFmtId="176" formatCode="#,##0_);[Red]\(#,##0\)"/>
   </numFmts>
   <fonts count="13">
     <font>
@@ -716,7 +720,7 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="177" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
@@ -1165,7 +1169,7 @@
         <a:effectLst/>
         <a:extLst>
           <a:ext uri="{AF507438-7753-43E0-B8FC-AC1667EBCBE1}">
-            <a14:hiddenEffects xmlns="" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+            <a14:hiddenEffects xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" xmlns="">
               <a:effectLst>
                 <a:outerShdw dist="35921" dir="2700000" algn="ctr" rotWithShape="0">
                   <a:srgbClr val="808080"/>
@@ -1207,7 +1211,7 @@
         <a:effectLst/>
         <a:extLst>
           <a:ext uri="{AF507438-7753-43E0-B8FC-AC1667EBCBE1}">
-            <a14:hiddenEffects xmlns="" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+            <a14:hiddenEffects xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" xmlns="">
               <a:effectLst>
                 <a:outerShdw dist="35921" dir="2700000" algn="ctr" rotWithShape="0">
                   <a:srgbClr val="808080"/>
@@ -1849,7 +1853,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="21.6640625" customWidth="1"/>
@@ -1878,6 +1882,11 @@
         <v>21</v>
       </c>
     </row>
+    <row r="4" spans="1:3">
+      <c r="A4" t="s">
+        <v>73</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/시험수수료표.xlsx
+++ b/시험수수료표.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="139">
   <si>
     <t>시험명</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -186,131 +186,391 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>세탁견뢰도</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>조직</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>질량</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>밀도</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>번수</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>망목수</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>필링</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>스낵성</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>파열강도</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>박리강도</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>접착강도</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>봉합강도</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>블로킹</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>사행도</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>마모강도(보호장갑)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>절단강도(BLADE)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>꿰뚤림강도(보호장갑)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>컷절단저항(TDM)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>방검성능3회기준</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>방호면적</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>볼버스팅법</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>유압법</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>가격유형</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>기본가격</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CHOIGODAEUN</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>재질</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>가죽감별</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>섬유혼용률</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(FT-IR/DSC)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>마모강도</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>KS K 0540</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>횟수</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>세탁견뢰도</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>일광견뢰도</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>급수</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>조직</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>질량</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>밀도</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>번수</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>망목수</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>필링</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>스낵성</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>파열강도</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>박리강도</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>접착강도</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>봉합강도</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>블로킹</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>사행도</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>마모강도(보호장갑)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>절단강도(BLADE)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>꿰뚤림강도(보호장갑)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>컷절단저항(TDM)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>방검성능3회기준</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>방호면적</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>볼버스팅법</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>유압법</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>시험명</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>시험방법</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>가격유형</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>기본가격</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>CHOIGODAEUN</t>
+    <t>Universal</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>드라이치수변화율</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>다리미질치수변화율</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>건열</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>증열분무</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>스팀프레스치수변화율</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>유연성</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>땀견뢰도</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>마찰견뢰도</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>물견뢰도</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>드라이클리닝견뢰도</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>해수견뢰도</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>투습도</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>건조속도</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>KS K 0642</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>KS K ISO 17617</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>흡수속도</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>섬유의수분제어성능</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>마찰대전성</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>반감기</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>표면저항</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>EN 1149-1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>내수도</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>저수압법</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>고수압법</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>정수압법</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>표면습윤저항성</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Spray</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>분데스만</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>보온성</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>열저항</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>접촉냉온감</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>흡습발영</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>공기투과도</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>방추도</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>신장율</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>방향1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>신장탄성율</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>정하중법</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>잔류변형율</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>섬도</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>섬도별구성비</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>발유도</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>오염제거성능</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>항균도</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>탈취성</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>자외선차단율</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>PH</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>폼알데하이드</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>아릴아민</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>유기주석화합물</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>방염제</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>알러지성염료함량</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>PFAS</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>강연도</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>굵기</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>길이</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>두께</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>비섬유질</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>인열강도</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>가연성</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>동적내수성</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>색차</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>적외선반사율</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>펜듈럼</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>텅법</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>일광및땀견뢰도</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -318,9 +578,8 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="1">
     <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
-    <numFmt numFmtId="176" formatCode="#,##0_);[Red]\(#,##0\)"/>
   </numFmts>
   <fonts count="13">
     <font>
@@ -369,13 +628,6 @@
     </font>
     <font>
       <b/>
-      <sz val="12"/>
-      <name val="돋움"/>
-      <family val="3"/>
-      <charset val="129"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
       <name val="돋움"/>
       <family val="3"/>
@@ -391,19 +643,26 @@
     </font>
     <font>
       <b/>
-      <sz val="12"/>
+      <sz val="9"/>
       <name val="굴림체"/>
       <family val="3"/>
       <charset val="129"/>
     </font>
     <font>
-      <sz val="10"/>
-      <name val="굴림체"/>
+      <b/>
+      <sz val="9"/>
+      <name val="돋움"/>
       <family val="3"/>
       <charset val="129"/>
     </font>
     <font>
-      <sz val="11"/>
+      <sz val="9"/>
+      <name val="돋움"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <sz val="9"/>
       <name val="굴림체"/>
       <family val="3"/>
       <charset val="129"/>
@@ -442,7 +701,7 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="124">
+  <cellStyleXfs count="125">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
@@ -708,27 +967,36 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="176" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="41" fontId="9" fillId="0" borderId="0" xfId="124" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="12" fillId="0" borderId="0" xfId="124" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="41" fontId="11" fillId="0" borderId="0" xfId="124" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="41" fontId="12" fillId="0" borderId="0" xfId="124" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="124">
+  <cellStyles count="125">
     <cellStyle name="20% - 강조색6 2" xfId="1"/>
     <cellStyle name="20% - 강조색6 2 2" xfId="2"/>
     <cellStyle name="20% - 강조색6 2 2 2" xfId="3"/>
@@ -750,6 +1018,7 @@
     <cellStyle name="20% - 강조색6 5 2 2" xfId="19"/>
     <cellStyle name="20% - 강조색6 5 2 3" xfId="20"/>
     <cellStyle name="Normal_MatricevalidpeinturesX85" xfId="21"/>
+    <cellStyle name="쉼표 [0]" xfId="124" builtinId="6"/>
     <cellStyle name="쉼표 [0] 10" xfId="122"/>
     <cellStyle name="쉼표 [0] 10 2" xfId="22"/>
     <cellStyle name="쉼표 [0] 10 3" xfId="23"/>
@@ -1169,7 +1438,7 @@
         <a:effectLst/>
         <a:extLst>
           <a:ext uri="{AF507438-7753-43E0-B8FC-AC1667EBCBE1}">
-            <a14:hiddenEffects xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" xmlns="">
+            <a14:hiddenEffects xmlns="" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
               <a:effectLst>
                 <a:outerShdw dist="35921" dir="2700000" algn="ctr" rotWithShape="0">
                   <a:srgbClr val="808080"/>
@@ -1211,7 +1480,7 @@
         <a:effectLst/>
         <a:extLst>
           <a:ext uri="{AF507438-7753-43E0-B8FC-AC1667EBCBE1}">
-            <a14:hiddenEffects xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" xmlns="">
+            <a14:hiddenEffects xmlns="" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
               <a:effectLst>
                 <a:outerShdw dist="35921" dir="2700000" algn="ctr" rotWithShape="0">
                   <a:srgbClr val="808080"/>
@@ -1231,470 +1500,1046 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D43"/>
-  <sheetFormatPr defaultRowHeight="13.5"/>
+  <dimension ref="A1:D126"/>
+  <sheetFormatPr defaultRowHeight="11.25"/>
   <cols>
-    <col min="1" max="1" width="22.6640625" customWidth="1"/>
-    <col min="2" max="2" width="22.33203125" customWidth="1"/>
+    <col min="1" max="1" width="22.6640625" style="4" customWidth="1"/>
+    <col min="2" max="2" width="22.33203125" style="4" customWidth="1"/>
+    <col min="3" max="3" width="8.88671875" style="4"/>
+    <col min="4" max="4" width="8.88671875" style="10"/>
+    <col min="5" max="16384" width="8.88671875" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" s="1" customFormat="1" ht="14.25">
-      <c r="A1" s="7" t="s">
+    <row r="1" spans="1:4" s="3" customFormat="1">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D1" s="8" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="B2" s="5"/>
+      <c r="C2" s="5"/>
+      <c r="D2" s="9">
+        <v>6000</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="B1" s="7" t="s">
+      <c r="B3" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="C1" s="7" t="s">
+      <c r="D3" s="10">
+        <v>50000</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="D4" s="10">
+        <v>50000</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="D5" s="10">
+        <v>40000</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="B6" s="5"/>
+      <c r="C6" s="5"/>
+      <c r="D6" s="11">
+        <v>100000</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="B7" s="5"/>
+      <c r="C7" s="5"/>
+      <c r="D7" s="11">
+        <v>50000</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="B8" s="5"/>
+      <c r="C8" s="5"/>
+      <c r="D8" s="11">
+        <v>35000</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="B9" s="5"/>
+      <c r="C9" s="5"/>
+      <c r="D9" s="11">
+        <v>70000</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="B10" s="5"/>
+      <c r="C10" s="5"/>
+      <c r="D10" s="11">
+        <v>35000</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4">
+      <c r="A11" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="B11" s="5"/>
+      <c r="C11" s="5"/>
+      <c r="D11" s="11">
+        <v>30000</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4">
+      <c r="A12" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="B12" s="5"/>
+      <c r="C12" s="5"/>
+      <c r="D12" s="11">
+        <v>15000</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4">
+      <c r="A13" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="B13" s="5"/>
+      <c r="C13" s="5"/>
+      <c r="D13" s="11">
+        <v>50000</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4">
+      <c r="A14" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="B14" s="5"/>
+      <c r="C14" s="5"/>
+      <c r="D14" s="11">
+        <v>15000</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4">
+      <c r="A15" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="B15" s="5"/>
+      <c r="C15" s="5"/>
+      <c r="D15" s="11">
+        <v>40000</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4">
+      <c r="A16" s="5" t="s">
+        <v>130</v>
+      </c>
+      <c r="B16" s="5"/>
+      <c r="C16" s="5"/>
+      <c r="D16" s="11">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4">
+      <c r="A17" s="5"/>
+      <c r="B17" s="5"/>
+      <c r="C17" s="5"/>
+      <c r="D17" s="11"/>
+    </row>
+    <row r="20" spans="1:4">
+      <c r="A20" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="B20" s="5"/>
+      <c r="C20" s="5"/>
+      <c r="D20" s="11">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4">
+      <c r="A21" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B21" s="5"/>
+      <c r="C21" s="5"/>
+      <c r="D21" s="11">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4">
+      <c r="A22" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B22" s="5"/>
+      <c r="C22" s="5"/>
+      <c r="D22" s="11">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4">
+      <c r="A23" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B23" s="5"/>
+      <c r="C23" s="5"/>
+      <c r="D23" s="11">
+        <v>15000</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4">
+      <c r="A24" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B24" s="5"/>
+      <c r="C24" s="5"/>
+      <c r="D24" s="9">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4">
+      <c r="A25" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="B25" s="7"/>
+      <c r="C25" s="7"/>
+      <c r="D25" s="11">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4">
+      <c r="A26" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="B26" s="7"/>
+      <c r="C26" s="7"/>
+      <c r="D26" s="11">
+        <v>8000</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4">
+      <c r="A27" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="B27" s="7"/>
+      <c r="C27" s="7"/>
+      <c r="D27" s="11">
+        <v>15000</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4">
+      <c r="A28" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="B28" s="7"/>
+      <c r="C28" s="7"/>
+      <c r="D28" s="11">
+        <v>8000</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4">
+      <c r="A29" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="B29" s="7"/>
+      <c r="C29" s="7"/>
+      <c r="D29" s="11">
+        <v>9000</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4">
+      <c r="A30" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="B30" s="7"/>
+      <c r="C30" s="7"/>
+      <c r="D30" s="11">
+        <v>9000</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4">
+      <c r="A31" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="B31" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="C31" s="7"/>
+      <c r="D31" s="11">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4">
+      <c r="A32" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="B32" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="C32" s="7"/>
+      <c r="D32" s="11">
+        <v>15000</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4">
+      <c r="A33" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="B33" s="7"/>
+      <c r="C33" s="7"/>
+      <c r="D33" s="11">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4">
+      <c r="A34" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="B34" s="7"/>
+      <c r="C34" s="7"/>
+      <c r="D34" s="11">
+        <v>19000</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4">
+      <c r="A35" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="B35" s="7"/>
+      <c r="C35" s="7"/>
+      <c r="D35" s="11">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4">
+      <c r="A36" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="B36" s="7"/>
+      <c r="C36" s="7"/>
+      <c r="D36" s="11">
+        <v>15000</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4">
+      <c r="A37" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="B37" s="7"/>
+      <c r="C37" s="7"/>
+      <c r="D37" s="11">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4">
+      <c r="A38" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="B38" s="7"/>
+      <c r="C38" s="7"/>
+      <c r="D38" s="11">
+        <v>38000</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4">
+      <c r="A39" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="B39" s="7"/>
+      <c r="C39" s="7"/>
+      <c r="D39" s="11">
+        <v>300000</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4">
+      <c r="A40" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="B40" s="7"/>
+      <c r="C40" s="7"/>
+      <c r="D40" s="11">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4">
+      <c r="A41" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="B41" s="7"/>
+      <c r="C41" s="7"/>
+      <c r="D41" s="11">
+        <v>500000</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4">
+      <c r="A42" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="B42" s="7"/>
+      <c r="C42" s="7"/>
+      <c r="D42" s="11">
+        <v>1400000</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4">
+      <c r="A43" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="B43" s="7"/>
+      <c r="C43" s="7"/>
+      <c r="D43" s="11">
+        <v>80000</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4">
+      <c r="A44" s="6" t="s">
+        <v>131</v>
+      </c>
+      <c r="B44" s="7" t="s">
+        <v>136</v>
+      </c>
+      <c r="C44" s="7"/>
+      <c r="D44" s="11">
+        <v>8000</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4">
+      <c r="A45" s="6" t="s">
+        <v>131</v>
+      </c>
+      <c r="B45" s="7" t="s">
+        <v>137</v>
+      </c>
+      <c r="C45" s="7"/>
+      <c r="D45" s="11">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4">
+      <c r="A46" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B46" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="C46" s="5"/>
+      <c r="D46" s="9">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4">
+      <c r="A47" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="B47" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="C47" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D47" s="9">
+        <v>18000</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4">
+      <c r="A48" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="B48" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="C48" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D48" s="9">
+        <v>30000</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4">
+      <c r="A49" s="4" t="s">
         <v>71</v>
       </c>
-      <c r="D1" s="7" t="s">
+      <c r="B49" s="4" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="2" spans="1:4">
-      <c r="A2" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B2" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="C2" s="6"/>
-      <c r="D2" s="6">
+      <c r="C49" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D49" s="10">
+        <v>18000</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4">
+      <c r="A50" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="D50" s="10">
+        <v>110000</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4">
+      <c r="A51" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="D51" s="10">
+        <v>12000</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4">
+      <c r="A52" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="B52" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="D52" s="10">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4">
+      <c r="A53" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="B53" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="D53" s="10">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4">
+      <c r="A54" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="B54" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="D54" s="10">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4">
+      <c r="A55" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="D55" s="10">
+        <v>15000</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4">
+      <c r="A56" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="D56" s="10">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4">
+      <c r="A57" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="D57" s="10">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4">
+      <c r="A58" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="D58" s="10">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4">
+      <c r="A59" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="D59" s="10">
+        <v>30000</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4">
+      <c r="A65" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="B65" s="5"/>
+      <c r="C65" s="5"/>
+      <c r="D65" s="9">
+        <v>9000</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4">
+      <c r="A66" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="B66" s="5"/>
+      <c r="C66" s="5"/>
+      <c r="D66" s="9">
+        <v>15000</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4">
+      <c r="A67" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="B67" s="5"/>
+      <c r="C67" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D67" s="9">
+        <v>6000</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4">
+      <c r="A68" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="B68" s="5"/>
+      <c r="C68" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D68" s="9">
+        <v>12000</v>
+      </c>
+    </row>
+    <row r="69" spans="1:4">
+      <c r="A69" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="D69" s="10">
+        <v>13000</v>
+      </c>
+    </row>
+    <row r="70" spans="1:4">
+      <c r="A70" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="B70" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="D70" s="10">
+        <v>7000</v>
+      </c>
+    </row>
+    <row r="71" spans="1:4">
+      <c r="A71" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="B71" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="D71" s="10">
+        <v>11000</v>
+      </c>
+    </row>
+    <row r="72" spans="1:4">
+      <c r="A72" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="D72" s="10">
+        <v>11000</v>
+      </c>
+    </row>
+    <row r="75" spans="1:4">
+      <c r="A75" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B75" s="5"/>
+      <c r="C75" s="5"/>
+      <c r="D75" s="9">
+        <v>7000</v>
+      </c>
+    </row>
+    <row r="76" spans="1:4">
+      <c r="A76" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B76" s="5"/>
+      <c r="C76" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="D76" s="9">
+        <v>7000</v>
+      </c>
+    </row>
+    <row r="77" spans="1:4">
+      <c r="A77" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="D77" s="10">
+        <v>9000</v>
+      </c>
+    </row>
+    <row r="78" spans="1:4">
+      <c r="A78" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="D78" s="10">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="79" spans="1:4">
+      <c r="A79" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="D79" s="10">
+        <v>7000</v>
+      </c>
+    </row>
+    <row r="80" spans="1:4">
+      <c r="A80" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="D80" s="10">
+        <v>9000</v>
+      </c>
+    </row>
+    <row r="81" spans="1:4">
+      <c r="A81" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="D81" s="10">
+        <v>8000</v>
+      </c>
+    </row>
+    <row r="82" spans="1:4">
+      <c r="A82" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="D82" s="10">
+        <v>12000</v>
+      </c>
+    </row>
+    <row r="85" spans="1:4">
+      <c r="A85" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="D85" s="10">
+        <v>40000</v>
+      </c>
+    </row>
+    <row r="86" spans="1:4">
+      <c r="A86" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="B86" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="D86" s="10">
+        <v>30000</v>
+      </c>
+    </row>
+    <row r="87" spans="1:4">
+      <c r="A87" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="B87" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="D87" s="10">
+        <v>50000</v>
+      </c>
+    </row>
+    <row r="88" spans="1:4">
+      <c r="A88" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="D88" s="10">
         <v>10000</v>
       </c>
     </row>
-    <row r="3" spans="1:4">
-      <c r="A3" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="B3" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="C3" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="D3" s="6">
-        <v>18000</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4">
-      <c r="A4" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="B4" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="C4" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="D4" s="6">
+    <row r="89" spans="1:4">
+      <c r="A89" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="D89" s="10">
+        <v>100000</v>
+      </c>
+    </row>
+    <row r="90" spans="1:4">
+      <c r="A90" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="D90" s="10">
+        <v>25000</v>
+      </c>
+    </row>
+    <row r="91" spans="1:4">
+      <c r="A91" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="D91" s="10">
+        <v>25000</v>
+      </c>
+    </row>
+    <row r="92" spans="1:4">
+      <c r="A92" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="D92" s="10">
         <v>30000</v>
       </c>
     </row>
-    <row r="5" spans="1:4">
-      <c r="A5" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="B5" s="6"/>
-      <c r="C5" s="6"/>
-      <c r="D5" s="6">
-        <v>7000</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4">
-      <c r="A6" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="B6" s="6"/>
-      <c r="C6" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="D6" s="6">
-        <v>7000</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4">
-      <c r="A7" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="B7" s="6"/>
-      <c r="C7" s="6"/>
-      <c r="D7" s="6">
-        <v>9000</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4">
-      <c r="A8" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="B8" s="6"/>
-      <c r="C8" s="6"/>
-      <c r="D8" s="6">
+    <row r="93" spans="1:4">
+      <c r="A93" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="B93" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="D93" s="10">
+        <v>100000</v>
+      </c>
+    </row>
+    <row r="94" spans="1:4">
+      <c r="A94" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="B94" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="D94" s="10">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="95" spans="1:4">
+      <c r="A95" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="B95" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="D95" s="10">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="96" spans="1:4">
+      <c r="A96" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="B96" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="D96" s="10">
+        <v>30000</v>
+      </c>
+    </row>
+    <row r="97" spans="1:4">
+      <c r="A97" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="B97" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="D97" s="10">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="98" spans="1:4">
+      <c r="A98" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="B98" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="D98" s="10">
+        <v>50000</v>
+      </c>
+    </row>
+    <row r="99" spans="1:4">
+      <c r="A99" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="D99" s="10">
+        <v>60000</v>
+      </c>
+    </row>
+    <row r="100" spans="1:4">
+      <c r="A100" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="D100" s="10">
+        <v>60000</v>
+      </c>
+    </row>
+    <row r="101" spans="1:4">
+      <c r="A101" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="D101" s="10">
+        <v>50000</v>
+      </c>
+    </row>
+    <row r="102" spans="1:4">
+      <c r="A102" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="D102" s="10">
+        <v>200000</v>
+      </c>
+    </row>
+    <row r="103" spans="1:4">
+      <c r="A103" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="D103" s="10">
+        <v>12000</v>
+      </c>
+    </row>
+    <row r="104" spans="1:4">
+      <c r="A104" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="D104" s="10">
+        <v>40000</v>
+      </c>
+    </row>
+    <row r="105" spans="1:4">
+      <c r="A105" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="D105" s="10">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="106" spans="1:4">
+      <c r="A106" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="D106" s="10">
+        <v>22000</v>
+      </c>
+    </row>
+    <row r="107" spans="1:4">
+      <c r="A107" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="D107" s="10">
         <v>15000</v>
       </c>
     </row>
-    <row r="9" spans="1:4">
-      <c r="A9" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="B9" s="6"/>
-      <c r="C9" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="D9" s="6">
-        <v>6000</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4">
-      <c r="A10" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="B10" s="6"/>
-      <c r="C10" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="D10" s="6">
-        <v>12000</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4">
-      <c r="A11" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="B11" s="6"/>
-      <c r="C11" s="6"/>
-      <c r="D11" s="6">
-        <v>6000</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4">
-      <c r="A12" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="B12" s="6"/>
-      <c r="C12" s="6"/>
-      <c r="D12" s="5">
-        <v>100000</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4">
-      <c r="A13" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="B13" s="6"/>
-      <c r="C13" s="6"/>
-      <c r="D13" s="5">
+    <row r="108" spans="1:4">
+      <c r="A108" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="D108" s="10">
+        <v>35000</v>
+      </c>
+    </row>
+    <row r="112" spans="1:4">
+      <c r="A112" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="D112" s="10">
+        <v>8000</v>
+      </c>
+    </row>
+    <row r="113" spans="1:4">
+      <c r="A113" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="D113" s="10">
+        <v>17000</v>
+      </c>
+    </row>
+    <row r="114" spans="1:4">
+      <c r="A114" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="D114" s="10">
+        <v>80000</v>
+      </c>
+    </row>
+    <row r="115" spans="1:4">
+      <c r="A115" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="D115" s="10">
+        <v>65000</v>
+      </c>
+    </row>
+    <row r="116" spans="1:4">
+      <c r="A116" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="D116" s="10">
+        <v>200000</v>
+      </c>
+    </row>
+    <row r="117" spans="1:4">
+      <c r="A117" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="D117" s="10">
+        <v>200000</v>
+      </c>
+    </row>
+    <row r="118" spans="1:4">
+      <c r="A118" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="D118" s="10">
+        <v>200000</v>
+      </c>
+    </row>
+    <row r="124" spans="1:4">
+      <c r="A124" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="D124" s="10">
         <v>50000</v>
       </c>
     </row>
-    <row r="14" spans="1:4">
-      <c r="A14" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="B14" s="6"/>
-      <c r="C14" s="6"/>
-      <c r="D14" s="5">
-        <v>35000</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4">
-      <c r="A15" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="B15" s="6"/>
-      <c r="C15" s="6"/>
-      <c r="D15" s="5">
-        <v>70000</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4">
-      <c r="A16" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="B16" s="6"/>
-      <c r="C16" s="6"/>
-      <c r="D16" s="5">
-        <v>35000</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4">
-      <c r="A17" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="B17" s="6"/>
-      <c r="C17" s="6"/>
-      <c r="D17" s="5">
-        <v>30000</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4">
-      <c r="A18" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="B18" s="6"/>
-      <c r="C18" s="6"/>
-      <c r="D18" s="5">
-        <v>15000</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4">
-      <c r="A19" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="B19" s="6"/>
-      <c r="C19" s="6"/>
-      <c r="D19" s="5">
-        <v>50000</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4">
-      <c r="A20" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="B20" s="6"/>
-      <c r="C20" s="6"/>
-      <c r="D20" s="5">
-        <v>10000</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4">
-      <c r="A21" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B21" s="6"/>
-      <c r="C21" s="6"/>
-      <c r="D21" s="5">
-        <v>10000</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4">
-      <c r="A22" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B22" s="6"/>
-      <c r="C22" s="6"/>
-      <c r="D22" s="5">
-        <v>10000</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4">
-      <c r="A23" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B23" s="6"/>
-      <c r="C23" s="6"/>
-      <c r="D23" s="5">
-        <v>15000</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4">
-      <c r="A24" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="B24" s="6"/>
-      <c r="C24" s="6"/>
-      <c r="D24" s="6">
-        <v>5000</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4">
-      <c r="A25" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="B25" s="3"/>
-      <c r="C25" s="3"/>
-      <c r="D25" s="5">
-        <v>4000</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4">
-      <c r="A26" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="B26" s="3"/>
-      <c r="C26" s="3"/>
-      <c r="D26" s="5">
-        <v>8000</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4">
-      <c r="A27" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="B27" s="3"/>
-      <c r="C27" s="3"/>
-      <c r="D27" s="5">
-        <v>15000</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4">
-      <c r="A28" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="B28" s="3"/>
-      <c r="C28" s="3"/>
-      <c r="D28" s="5">
-        <v>8000</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4">
-      <c r="A29" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="B29" s="3"/>
-      <c r="C29" s="3"/>
-      <c r="D29" s="5">
-        <v>9000</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4">
-      <c r="A30" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="B30" s="3"/>
-      <c r="C30" s="3"/>
-      <c r="D30" s="5">
-        <v>9000</v>
-      </c>
-    </row>
-    <row r="31" spans="1:4">
-      <c r="A31" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="B31" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="C31" s="3"/>
-      <c r="D31" s="5">
-        <v>10000</v>
-      </c>
-    </row>
-    <row r="32" spans="1:4">
-      <c r="A32" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="B32" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="C32" s="3"/>
-      <c r="D32" s="5">
-        <v>15000</v>
-      </c>
-    </row>
-    <row r="33" spans="1:4">
-      <c r="A33" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="B33" s="3"/>
-      <c r="C33" s="3"/>
-      <c r="D33" s="5">
-        <v>10000</v>
-      </c>
-    </row>
-    <row r="34" spans="1:4">
-      <c r="A34" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="B34" s="3"/>
-      <c r="C34" s="3"/>
-      <c r="D34" s="5">
-        <v>19000</v>
-      </c>
-    </row>
-    <row r="35" spans="1:4">
-      <c r="A35" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="B35" s="3"/>
-      <c r="C35" s="3"/>
-      <c r="D35" s="5">
-        <v>10000</v>
-      </c>
-    </row>
-    <row r="36" spans="1:4">
-      <c r="A36" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="B36" s="3"/>
-      <c r="C36" s="3"/>
-      <c r="D36" s="5">
-        <v>15000</v>
-      </c>
-    </row>
-    <row r="37" spans="1:4">
-      <c r="A37" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="B37" s="3"/>
-      <c r="C37" s="3"/>
-      <c r="D37" s="5">
-        <v>20000</v>
-      </c>
-    </row>
-    <row r="38" spans="1:4">
-      <c r="A38" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="B38" s="3"/>
-      <c r="C38" s="3"/>
-      <c r="D38" s="5">
-        <v>38000</v>
-      </c>
-    </row>
-    <row r="39" spans="1:4">
-      <c r="A39" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="B39" s="3"/>
-      <c r="C39" s="3"/>
-      <c r="D39" s="5">
-        <v>300000</v>
-      </c>
-    </row>
-    <row r="40" spans="1:4">
-      <c r="A40" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="B40" s="3"/>
-      <c r="C40" s="3"/>
-      <c r="D40" s="5">
-        <v>10000</v>
-      </c>
-    </row>
-    <row r="41" spans="1:4">
-      <c r="A41" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="B41" s="3"/>
-      <c r="C41" s="3"/>
-      <c r="D41" s="5">
-        <v>500000</v>
-      </c>
-    </row>
-    <row r="42" spans="1:4">
-      <c r="A42" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="B42" s="3"/>
-      <c r="C42" s="3"/>
-      <c r="D42" s="5">
-        <v>1400000</v>
-      </c>
-    </row>
-    <row r="43" spans="1:4">
-      <c r="A43" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="B43" s="3"/>
-      <c r="C43" s="3"/>
-      <c r="D43" s="5">
-        <v>80000</v>
+    <row r="125" spans="1:4">
+      <c r="A125" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="D125" s="10">
+        <v>180000</v>
+      </c>
+    </row>
+    <row r="126" spans="1:4">
+      <c r="A126" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="D126" s="10">
+        <v>130000</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -1706,26 +2551,26 @@
     <col min="2" max="2" width="20.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" s="2" customFormat="1">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:7" s="1" customFormat="1">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="1" t="s">
         <v>8</v>
       </c>
     </row>
@@ -1861,30 +2706,30 @@
     <col min="3" max="3" width="37.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" s="2" customFormat="1">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:3" s="1" customFormat="1">
+      <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="2" spans="1:3">
       <c r="A2" t="s">
-        <v>13</v>
+        <v>66</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" t="s">
-        <v>73</v>
+        <v>21</v>
       </c>
     </row>
   </sheetData>
